--- a/excell/home_page.xlsx
+++ b/excell/home_page.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\Home Page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A31F7AD-C3F3-4509-A22F-5EB82A28E8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26891BFC-0BC8-4655-BADF-C0B4AD34DFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7A99A404-56C1-468B-8E6E-E2513DBB1230}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Year</t>
   </si>
@@ -53,15 +53,6 @@
     <t>Co-chair</t>
   </si>
   <si>
-    <t>Cincinnati, Ohio</t>
-  </si>
-  <si>
-    <t>Rashmi Jha</t>
-  </si>
-  <si>
-    <t>Soumyajit Mandal</t>
-  </si>
-  <si>
     <t>Lafayette, Louisiana</t>
   </si>
   <si>
@@ -92,18 +83,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>513-556-1361</t>
-  </si>
-  <si>
-    <t>rashmi.jha@uc.edu</t>
-  </si>
-  <si>
-    <t>413-782-1274</t>
-  </si>
-  <si>
-    <t>smandal@bnl.gov</t>
-  </si>
-  <si>
     <t>337-482-6568</t>
   </si>
   <si>
@@ -137,10 +116,43 @@
     <t>Website</t>
   </si>
   <si>
-    <t>https://mwscas2026.org/</t>
-  </si>
-  <si>
     <t>https://ieee-cas.org/event/conference/2027-ieee-international-midwest-symposium-circuits-and-systems</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>Buffalo, New York</t>
+  </si>
+  <si>
+    <t>Bibhu Sahoo</t>
+  </si>
+  <si>
+    <t>Jeffery Walling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 716- 645-9166</t>
+  </si>
+  <si>
+    <t>bibhu@buffalo.edu</t>
+  </si>
+  <si>
+    <t>540-231-4786</t>
+  </si>
+  <si>
+    <t>jswalling@vt.edu</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Welcome to MWSCAS</t>
+  </si>
+  <si>
+    <t>Established in 1955, the IEEE International Midwest Symposium on Circuits and Systems (MWSCAS) has served the circuits and systems community for seven decades.</t>
   </si>
 </sst>
 </file>
@@ -546,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C028CDB6-6526-4FB9-9E02-00EBEB49CF73}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="5"/>
@@ -560,149 +572,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>2027</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>2027</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>2028</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>2029</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>30</v>
+      <c r="H7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{9C6984D9-252B-48DA-A898-641105289E39}"/>
-    <hyperlink ref="I2" r:id="rId2" xr:uid="{9AE17C8F-8532-4D73-8E63-D8226795FF1D}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{8A866231-7887-4A7D-B3D4-85CC58FA1A85}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{C82E620B-A958-42C2-A6DF-864757870A43}"/>
-    <hyperlink ref="I4" r:id="rId5" xr:uid="{BC2966C2-7C48-43CD-8F57-2D16381A6947}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{B3DA9A0E-AE98-427B-95FC-AD40315C086A}"/>
-    <hyperlink ref="I5" r:id="rId7" xr:uid="{F4207C02-91C6-4AA5-9100-678DCFB849CC}"/>
-    <hyperlink ref="C2" r:id="rId8" xr:uid="{451F8A9A-FD91-4AD2-990D-1ACC0B87EE5E}"/>
-    <hyperlink ref="C3" r:id="rId9" xr:uid="{2541F08C-872E-47BD-9B62-EF4CD4D8EDFA}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{8A866231-7887-4A7D-B3D4-85CC58FA1A85}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{C82E620B-A958-42C2-A6DF-864757870A43}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{BC2966C2-7C48-43CD-8F57-2D16381A6947}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{B3DA9A0E-AE98-427B-95FC-AD40315C086A}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{F4207C02-91C6-4AA5-9100-678DCFB849CC}"/>
+    <hyperlink ref="C4" r:id="rId6" xr:uid="{2541F08C-872E-47BD-9B62-EF4CD4D8EDFA}"/>
+    <hyperlink ref="F7" r:id="rId7" xr:uid="{418EFA4B-DEE6-455B-B143-99D151EEC70C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
